--- a/ig/DM-MARS-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1160,6 +1160,12 @@
   </si>
   <si>
     <t>Autre service territorial</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
   </si>
   <si>
     <t/>
@@ -1454,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B180"/>
+  <dimension ref="A1:B181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2890,15 +2896,23 @@
         <v>382</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>384</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2939,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -2933,42 +2947,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
